--- a/data-source/consumo.xlsx
+++ b/data-source/consumo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/STK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{50E79B7A-AFAB-49C4-9F58-DB4B3C2354E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B3D4EF1-4570-4722-BF02-28E0D68714EE}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{50E79B7A-AFAB-49C4-9F58-DB4B3C2354E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72E424A3-974C-442E-AF8C-D975A1C19CA1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2839" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="139">
   <si>
     <t>Cód.prod</t>
   </si>
@@ -463,6 +463,7 @@
       <sz val="11"/>
       <color rgb="FF800000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -30916,10 +30917,10 @@
         <v>7</v>
       </c>
       <c r="F1307" s="4">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="G1307" s="5">
-        <v>46262</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.3">
@@ -30939,10 +30940,10 @@
         <v>7</v>
       </c>
       <c r="F1308" s="4">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="G1308" s="5">
-        <v>46190</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="1309" spans="1:7" x14ac:dyDescent="0.3">
@@ -30962,10 +30963,10 @@
         <v>7</v>
       </c>
       <c r="F1309" s="4">
-        <v>488.4</v>
+        <v>34</v>
       </c>
       <c r="G1309" s="5">
-        <v>46287</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1310" spans="1:7" x14ac:dyDescent="0.3">
@@ -30985,10 +30986,10 @@
         <v>7</v>
       </c>
       <c r="F1310" s="4">
-        <v>492</v>
+        <v>39</v>
       </c>
       <c r="G1310" s="5">
-        <v>46239</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.3">
@@ -31008,10 +31009,10 @@
         <v>7</v>
       </c>
       <c r="F1311" s="4">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="G1311" s="5">
-        <v>46239</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.3">
@@ -31031,10 +31032,10 @@
         <v>7</v>
       </c>
       <c r="F1312" s="4">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="G1312" s="5">
-        <v>46262</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1313" spans="1:7" x14ac:dyDescent="0.3">
@@ -31054,10 +31055,10 @@
         <v>7</v>
       </c>
       <c r="F1313" s="4">
-        <v>500</v>
+        <v>111.4</v>
       </c>
       <c r="G1313" s="5">
-        <v>46262</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.3">
@@ -31077,18 +31078,18 @@
         <v>7</v>
       </c>
       <c r="F1314" s="4">
-        <v>504</v>
+        <v>120</v>
       </c>
       <c r="G1314" s="5">
-        <v>46287</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1315" s="2">
-        <v>20023</v>
+        <v>20021</v>
       </c>
       <c r="B1315" s="3" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="C1315" s="2">
         <v>39</v>
@@ -31100,18 +31101,18 @@
         <v>7</v>
       </c>
       <c r="F1315" s="4">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="G1315" s="5">
-        <v>46190</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1316" s="2">
-        <v>20023</v>
+        <v>20021</v>
       </c>
       <c r="B1316" s="3" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="C1316" s="2">
         <v>39</v>
@@ -31123,18 +31124,18 @@
         <v>7</v>
       </c>
       <c r="F1316" s="4">
-        <v>40</v>
+        <v>477</v>
       </c>
       <c r="G1316" s="5">
-        <v>46141</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1317" s="2">
-        <v>20025</v>
+        <v>20021</v>
       </c>
       <c r="B1317" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="C1317" s="2">
         <v>39</v>
@@ -31146,18 +31147,18 @@
         <v>7</v>
       </c>
       <c r="F1317" s="4">
-        <v>40</v>
+        <v>488.4</v>
       </c>
       <c r="G1317" s="5">
-        <v>45967</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1318" s="2">
-        <v>20026</v>
+        <v>20021</v>
       </c>
       <c r="B1318" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="C1318" s="2">
         <v>39</v>
@@ -31169,18 +31170,18 @@
         <v>7</v>
       </c>
       <c r="F1318" s="4">
-        <v>80</v>
+        <v>492</v>
       </c>
       <c r="G1318" s="5">
-        <v>45953</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1319" s="2">
-        <v>20028</v>
+        <v>20021</v>
       </c>
       <c r="B1319" s="3" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="C1319" s="2">
         <v>39</v>
@@ -31192,18 +31193,18 @@
         <v>7</v>
       </c>
       <c r="F1319" s="4">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="G1319" s="5">
-        <v>46072</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1320" s="2">
-        <v>20034</v>
+        <v>20021</v>
       </c>
       <c r="B1320" s="3" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C1320" s="2">
         <v>39</v>
@@ -31215,18 +31216,18 @@
         <v>7</v>
       </c>
       <c r="F1320" s="4">
-        <v>198</v>
+        <v>500</v>
       </c>
       <c r="G1320" s="5">
-        <v>46308</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1321" s="2">
-        <v>20034</v>
+        <v>20021</v>
       </c>
       <c r="B1321" s="3" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C1321" s="2">
         <v>39</v>
@@ -31238,18 +31239,18 @@
         <v>7</v>
       </c>
       <c r="F1321" s="4">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="G1321" s="5">
-        <v>46283</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1322" s="2">
-        <v>20034</v>
+        <v>20021</v>
       </c>
       <c r="B1322" s="3" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C1322" s="2">
         <v>39</v>
@@ -31261,18 +31262,18 @@
         <v>7</v>
       </c>
       <c r="F1322" s="4">
-        <v>479.8</v>
+        <v>504</v>
       </c>
       <c r="G1322" s="5">
-        <v>46297</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1323" s="2">
-        <v>20034</v>
+        <v>20023</v>
       </c>
       <c r="B1323" s="3" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="C1323" s="2">
         <v>39</v>
@@ -31284,18 +31285,18 @@
         <v>7</v>
       </c>
       <c r="F1323" s="4">
-        <v>517</v>
+        <v>29</v>
       </c>
       <c r="G1323" s="5">
-        <v>46283</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1324" s="2">
-        <v>20034</v>
+        <v>20023</v>
       </c>
       <c r="B1324" s="3" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="C1324" s="2">
         <v>39</v>
@@ -31307,18 +31308,18 @@
         <v>7</v>
       </c>
       <c r="F1324" s="4">
-        <v>522</v>
+        <v>40</v>
       </c>
       <c r="G1324" s="5">
-        <v>46297</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1325" s="2">
-        <v>20034</v>
+        <v>20025</v>
       </c>
       <c r="B1325" s="3" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="C1325" s="2">
         <v>39</v>
@@ -31330,18 +31331,18 @@
         <v>7</v>
       </c>
       <c r="F1325" s="4">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="G1325" s="5">
-        <v>46259</v>
+        <v>45967</v>
       </c>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1326" s="2">
-        <v>20035</v>
+        <v>20026</v>
       </c>
       <c r="B1326" s="3" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="C1326" s="2">
         <v>39</v>
@@ -31353,18 +31354,18 @@
         <v>7</v>
       </c>
       <c r="F1326" s="4">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G1326" s="5">
-        <v>46303</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1327" s="2">
-        <v>20035</v>
+        <v>20028</v>
       </c>
       <c r="B1327" s="3" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="C1327" s="2">
         <v>39</v>
@@ -31376,18 +31377,18 @@
         <v>7</v>
       </c>
       <c r="F1327" s="4">
-        <v>412</v>
+        <v>120</v>
       </c>
       <c r="G1327" s="5">
-        <v>46303</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1328" s="2">
-        <v>20035</v>
+        <v>20034</v>
       </c>
       <c r="B1328" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1328" s="2">
         <v>39</v>
@@ -31399,18 +31400,18 @@
         <v>7</v>
       </c>
       <c r="F1328" s="4">
-        <v>489</v>
+        <v>198</v>
       </c>
       <c r="G1328" s="5">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1329" s="2">
-        <v>20035</v>
+        <v>20034</v>
       </c>
       <c r="B1329" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1329" s="2">
         <v>39</v>
@@ -31422,18 +31423,18 @@
         <v>7</v>
       </c>
       <c r="F1329" s="4">
-        <v>505</v>
+        <v>477</v>
       </c>
       <c r="G1329" s="5">
-        <v>46303</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="1330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1330" s="2">
-        <v>20035</v>
+        <v>20034</v>
       </c>
       <c r="B1330" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1330" s="2">
         <v>39</v>
@@ -31445,18 +31446,18 @@
         <v>7</v>
       </c>
       <c r="F1330" s="4">
-        <v>506</v>
+        <v>479.8</v>
       </c>
       <c r="G1330" s="5">
-        <v>46303</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1331" s="2">
-        <v>20035</v>
+        <v>20034</v>
       </c>
       <c r="B1331" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1331" s="2">
         <v>39</v>
@@ -31468,18 +31469,18 @@
         <v>7</v>
       </c>
       <c r="F1331" s="4">
-        <v>1000</v>
+        <v>517</v>
       </c>
       <c r="G1331" s="5">
-        <v>46265</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1332" s="2">
-        <v>20036</v>
+        <v>20034</v>
       </c>
       <c r="B1332" s="3" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="C1332" s="2">
         <v>39</v>
@@ -31491,18 +31492,18 @@
         <v>7</v>
       </c>
       <c r="F1332" s="4">
-        <v>31</v>
+        <v>522</v>
       </c>
       <c r="G1332" s="5">
-        <v>46080</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1333" s="2">
-        <v>20036</v>
+        <v>20034</v>
       </c>
       <c r="B1333" s="3" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="C1333" s="2">
         <v>39</v>
@@ -31514,18 +31515,18 @@
         <v>7</v>
       </c>
       <c r="F1333" s="4">
-        <v>40</v>
+        <v>2000</v>
       </c>
       <c r="G1333" s="5">
-        <v>45992</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1334" s="2">
-        <v>20036</v>
+        <v>20035</v>
       </c>
       <c r="B1334" s="3" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C1334" s="2">
         <v>39</v>
@@ -31537,18 +31538,18 @@
         <v>7</v>
       </c>
       <c r="F1334" s="4">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="G1334" s="5">
-        <v>45992</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1335" s="2">
-        <v>20036</v>
+        <v>20035</v>
       </c>
       <c r="B1335" s="3" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C1335" s="2">
         <v>39</v>
@@ -31560,18 +31561,18 @@
         <v>7</v>
       </c>
       <c r="F1335" s="4">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="G1335" s="5">
-        <v>46045</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="1336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1336" s="2">
-        <v>20036</v>
+        <v>20035</v>
       </c>
       <c r="B1336" s="3" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C1336" s="2">
         <v>39</v>
@@ -31583,18 +31584,18 @@
         <v>7</v>
       </c>
       <c r="F1336" s="4">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="G1336" s="5">
-        <v>45992</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1337" s="2">
-        <v>20036</v>
+        <v>20035</v>
       </c>
       <c r="B1337" s="3" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C1337" s="2">
         <v>39</v>
@@ -31606,18 +31607,18 @@
         <v>7</v>
       </c>
       <c r="F1337" s="4">
-        <v>80</v>
+        <v>489</v>
       </c>
       <c r="G1337" s="5">
-        <v>46080</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1338" s="2">
-        <v>20036</v>
+        <v>20035</v>
       </c>
       <c r="B1338" s="3" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C1338" s="2">
         <v>39</v>
@@ -31629,18 +31630,18 @@
         <v>7</v>
       </c>
       <c r="F1338" s="4">
-        <v>89</v>
+        <v>505</v>
       </c>
       <c r="G1338" s="5">
-        <v>46080</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1339" s="2">
-        <v>20036</v>
+        <v>20035</v>
       </c>
       <c r="B1339" s="3" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C1339" s="2">
         <v>39</v>
@@ -31652,18 +31653,18 @@
         <v>7</v>
       </c>
       <c r="F1339" s="4">
-        <v>119.4</v>
+        <v>506</v>
       </c>
       <c r="G1339" s="5">
-        <v>46076</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1340" s="2">
-        <v>20036</v>
+        <v>20035</v>
       </c>
       <c r="B1340" s="3" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C1340" s="2">
         <v>39</v>
@@ -31675,10 +31676,10 @@
         <v>7</v>
       </c>
       <c r="F1340" s="4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="G1340" s="5">
-        <v>45992</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.3">
@@ -31698,10 +31699,10 @@
         <v>7</v>
       </c>
       <c r="F1341" s="4">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="G1341" s="5">
-        <v>46111</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.3">
@@ -31721,18 +31722,18 @@
         <v>7</v>
       </c>
       <c r="F1342" s="4">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="G1342" s="5">
-        <v>46209</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="1343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1343" s="2">
-        <v>20043</v>
+        <v>20036</v>
       </c>
       <c r="B1343" s="3" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="C1343" s="2">
         <v>39</v>
@@ -31744,18 +31745,18 @@
         <v>7</v>
       </c>
       <c r="F1343" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G1343" s="5">
-        <v>46262</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1344" s="2">
-        <v>20043</v>
+        <v>20036</v>
       </c>
       <c r="B1344" s="3" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="C1344" s="2">
         <v>39</v>
@@ -31767,18 +31768,18 @@
         <v>7</v>
       </c>
       <c r="F1344" s="4">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="G1344" s="5">
-        <v>46269</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="1345" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1345" s="2">
-        <v>20077</v>
+        <v>20036</v>
       </c>
       <c r="B1345" s="3" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C1345" s="2">
         <v>39</v>
@@ -31790,18 +31791,18 @@
         <v>7</v>
       </c>
       <c r="F1345" s="4">
-        <v>199.5</v>
+        <v>80</v>
       </c>
       <c r="G1345" s="5">
-        <v>46276</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346" s="2">
-        <v>20078</v>
+        <v>20036</v>
       </c>
       <c r="B1346" s="3" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="C1346" s="2">
         <v>39</v>
@@ -31813,18 +31814,18 @@
         <v>7</v>
       </c>
       <c r="F1346" s="4">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="G1346" s="5">
-        <v>46276</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1347" s="2">
-        <v>20082</v>
+        <v>20036</v>
       </c>
       <c r="B1347" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C1347" s="2">
         <v>39</v>
@@ -31836,18 +31837,18 @@
         <v>7</v>
       </c>
       <c r="F1347" s="4">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="G1347" s="5">
-        <v>46148</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="1348" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1348" s="2">
-        <v>20082</v>
+        <v>20036</v>
       </c>
       <c r="B1348" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C1348" s="2">
         <v>39</v>
@@ -31859,18 +31860,18 @@
         <v>7</v>
       </c>
       <c r="F1348" s="4">
-        <v>4</v>
+        <v>119.4</v>
       </c>
       <c r="G1348" s="5">
-        <v>46183</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1349" s="2">
-        <v>20082</v>
+        <v>20036</v>
       </c>
       <c r="B1349" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C1349" s="2">
         <v>39</v>
@@ -31882,18 +31883,18 @@
         <v>7</v>
       </c>
       <c r="F1349" s="4">
-        <v>4.8</v>
+        <v>160</v>
       </c>
       <c r="G1349" s="5">
-        <v>46184</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1350" s="2">
-        <v>20082</v>
+        <v>20036</v>
       </c>
       <c r="B1350" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C1350" s="2">
         <v>39</v>
@@ -31905,18 +31906,18 @@
         <v>7</v>
       </c>
       <c r="F1350" s="4">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="G1350" s="5">
-        <v>46287</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="1351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1351" s="2">
-        <v>20082</v>
+        <v>20036</v>
       </c>
       <c r="B1351" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C1351" s="2">
         <v>39</v>
@@ -31928,18 +31929,18 @@
         <v>7</v>
       </c>
       <c r="F1351" s="4">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="G1351" s="5">
-        <v>46300</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="1352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1352" s="2">
-        <v>20082</v>
+        <v>20043</v>
       </c>
       <c r="B1352" s="3" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="C1352" s="2">
         <v>39</v>
@@ -31951,18 +31952,18 @@
         <v>7</v>
       </c>
       <c r="F1352" s="4">
-        <v>9.8000000000000007</v>
+        <v>100</v>
       </c>
       <c r="G1352" s="5">
-        <v>46148</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="1353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1353" s="2">
-        <v>20082</v>
+        <v>20043</v>
       </c>
       <c r="B1353" s="3" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="C1353" s="2">
         <v>39</v>
@@ -31974,18 +31975,18 @@
         <v>7</v>
       </c>
       <c r="F1353" s="4">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="G1353" s="5">
-        <v>46211</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1354" s="2">
-        <v>20082</v>
+        <v>20077</v>
       </c>
       <c r="B1354" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C1354" s="2">
         <v>39</v>
@@ -31997,18 +31998,18 @@
         <v>7</v>
       </c>
       <c r="F1354" s="4">
-        <v>22</v>
+        <v>199.5</v>
       </c>
       <c r="G1354" s="5">
-        <v>46100</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="1355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1355" s="2">
-        <v>20082</v>
+        <v>20078</v>
       </c>
       <c r="B1355" s="3" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="C1355" s="2">
         <v>39</v>
@@ -32020,10 +32021,10 @@
         <v>7</v>
       </c>
       <c r="F1355" s="4">
-        <v>43.4</v>
+        <v>199</v>
       </c>
       <c r="G1355" s="5">
-        <v>46150</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="1356" spans="1:7" x14ac:dyDescent="0.3">
@@ -32043,10 +32044,10 @@
         <v>7</v>
       </c>
       <c r="F1356" s="4">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="G1356" s="5">
-        <v>46135</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="1357" spans="1:7" x14ac:dyDescent="0.3">
@@ -32066,10 +32067,10 @@
         <v>7</v>
       </c>
       <c r="F1357" s="4">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G1357" s="5">
-        <v>46216</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.3">
@@ -32089,10 +32090,10 @@
         <v>7</v>
       </c>
       <c r="F1358" s="4">
-        <v>148</v>
+        <v>4.8</v>
       </c>
       <c r="G1358" s="5">
-        <v>46135</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.3">
@@ -32112,10 +32113,10 @@
         <v>7</v>
       </c>
       <c r="F1359" s="4">
-        <v>152.6</v>
+        <v>5</v>
       </c>
       <c r="G1359" s="5">
-        <v>46150</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.3">
@@ -32135,10 +32136,10 @@
         <v>7</v>
       </c>
       <c r="F1360" s="4">
-        <v>196.6</v>
+        <v>5</v>
       </c>
       <c r="G1360" s="5">
-        <v>46127</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="1361" spans="1:7" x14ac:dyDescent="0.3">
@@ -32158,10 +32159,10 @@
         <v>7</v>
       </c>
       <c r="F1361" s="4">
-        <v>214.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="G1361" s="5">
-        <v>46184</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="1362" spans="1:7" x14ac:dyDescent="0.3">
@@ -32181,10 +32182,10 @@
         <v>7</v>
       </c>
       <c r="F1362" s="4">
-        <v>279.60000000000002</v>
+        <v>11</v>
       </c>
       <c r="G1362" s="5">
-        <v>46113</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="1363" spans="1:7" x14ac:dyDescent="0.3">
@@ -32204,10 +32205,10 @@
         <v>7</v>
       </c>
       <c r="F1363" s="4">
-        <v>300</v>
+        <v>22</v>
       </c>
       <c r="G1363" s="5">
-        <v>46253</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.3">
@@ -32227,10 +32228,10 @@
         <v>7</v>
       </c>
       <c r="F1364" s="4">
-        <v>300.8</v>
+        <v>43.4</v>
       </c>
       <c r="G1364" s="5">
-        <v>46183</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.3">
@@ -32250,10 +32251,10 @@
         <v>7</v>
       </c>
       <c r="F1365" s="4">
-        <v>347.4</v>
+        <v>46</v>
       </c>
       <c r="G1365" s="5">
-        <v>46184</v>
+        <v>46135</v>
       </c>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.3">
@@ -32273,10 +32274,10 @@
         <v>7</v>
       </c>
       <c r="F1366" s="4">
-        <v>396</v>
+        <v>100</v>
       </c>
       <c r="G1366" s="5">
-        <v>46197</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.3">
@@ -32296,10 +32297,10 @@
         <v>7</v>
       </c>
       <c r="F1367" s="4">
-        <v>399</v>
+        <v>148</v>
       </c>
       <c r="G1367" s="5">
-        <v>46141</v>
+        <v>46135</v>
       </c>
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.3">
@@ -32319,10 +32320,10 @@
         <v>7</v>
       </c>
       <c r="F1368" s="4">
-        <v>400</v>
+        <v>152.6</v>
       </c>
       <c r="G1368" s="5">
-        <v>46300</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.3">
@@ -32342,10 +32343,10 @@
         <v>7</v>
       </c>
       <c r="F1369" s="4">
-        <v>478</v>
+        <v>196.6</v>
       </c>
       <c r="G1369" s="5">
-        <v>46220</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.3">
@@ -32365,10 +32366,10 @@
         <v>7</v>
       </c>
       <c r="F1370" s="4">
-        <v>484</v>
+        <v>214.8</v>
       </c>
       <c r="G1370" s="5">
-        <v>46206</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="1371" spans="1:7" x14ac:dyDescent="0.3">
@@ -32388,10 +32389,10 @@
         <v>7</v>
       </c>
       <c r="F1371" s="4">
-        <v>485</v>
+        <v>279.60000000000002</v>
       </c>
       <c r="G1371" s="5">
-        <v>46300</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1372" spans="1:7" x14ac:dyDescent="0.3">
@@ -32411,10 +32412,10 @@
         <v>7</v>
       </c>
       <c r="F1372" s="4">
-        <v>490</v>
+        <v>300</v>
       </c>
       <c r="G1372" s="5">
-        <v>46268</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.3">
@@ -32434,10 +32435,10 @@
         <v>7</v>
       </c>
       <c r="F1373" s="4">
-        <v>490</v>
+        <v>300.8</v>
       </c>
       <c r="G1373" s="5">
-        <v>46287</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.3">
@@ -32457,10 +32458,10 @@
         <v>7</v>
       </c>
       <c r="F1374" s="4">
-        <v>491</v>
+        <v>347.4</v>
       </c>
       <c r="G1374" s="5">
-        <v>46220</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.3">
@@ -32480,10 +32481,10 @@
         <v>7</v>
       </c>
       <c r="F1375" s="4">
-        <v>499.2</v>
+        <v>396</v>
       </c>
       <c r="G1375" s="5">
-        <v>46148</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.3">
@@ -32503,10 +32504,10 @@
         <v>7</v>
       </c>
       <c r="F1376" s="4">
-        <v>500</v>
+        <v>399</v>
       </c>
       <c r="G1376" s="5">
-        <v>46211</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="1377" spans="1:7" x14ac:dyDescent="0.3">
@@ -32526,10 +32527,10 @@
         <v>7</v>
       </c>
       <c r="F1377" s="4">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G1377" s="5">
-        <v>46220</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="1378" spans="1:7" x14ac:dyDescent="0.3">
@@ -32549,10 +32550,10 @@
         <v>7</v>
       </c>
       <c r="F1378" s="4">
-        <v>510</v>
+        <v>400</v>
       </c>
       <c r="G1378" s="5">
-        <v>46300</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="1379" spans="1:7" x14ac:dyDescent="0.3">
@@ -32572,10 +32573,10 @@
         <v>7</v>
       </c>
       <c r="F1379" s="4">
-        <v>513.6</v>
+        <v>478</v>
       </c>
       <c r="G1379" s="5">
-        <v>46206</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="1380" spans="1:7" x14ac:dyDescent="0.3">
@@ -32595,10 +32596,10 @@
         <v>7</v>
       </c>
       <c r="F1380" s="4">
-        <v>517</v>
+        <v>484</v>
       </c>
       <c r="G1380" s="5">
-        <v>46220</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="1381" spans="1:7" x14ac:dyDescent="0.3">
@@ -32618,10 +32619,10 @@
         <v>7</v>
       </c>
       <c r="F1381" s="4">
-        <v>633</v>
+        <v>485</v>
       </c>
       <c r="G1381" s="5">
-        <v>46184</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="1382" spans="1:7" x14ac:dyDescent="0.3">
@@ -32641,10 +32642,10 @@
         <v>7</v>
       </c>
       <c r="F1382" s="4">
-        <v>795.2</v>
+        <v>486</v>
       </c>
       <c r="G1382" s="5">
-        <v>46183</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="1383" spans="1:7" x14ac:dyDescent="0.3">
@@ -32664,18 +32665,18 @@
         <v>7</v>
       </c>
       <c r="F1383" s="4">
-        <v>2000</v>
+        <v>490</v>
       </c>
       <c r="G1383" s="5">
-        <v>46265</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="1384" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1384" s="2">
-        <v>20084</v>
+        <v>20082</v>
       </c>
       <c r="B1384" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C1384" s="2">
         <v>39</v>
@@ -32687,18 +32688,18 @@
         <v>7</v>
       </c>
       <c r="F1384" s="4">
-        <v>997</v>
+        <v>490</v>
       </c>
       <c r="G1384" s="5">
-        <v>46267</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="1385" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1385" s="2">
-        <v>20088</v>
+        <v>20082</v>
       </c>
       <c r="B1385" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C1385" s="2">
         <v>39</v>
@@ -32710,18 +32711,18 @@
         <v>7</v>
       </c>
       <c r="F1385" s="4">
-        <v>217</v>
+        <v>491</v>
       </c>
       <c r="G1385" s="5">
-        <v>46297</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="1386" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1386" s="2">
-        <v>20088</v>
+        <v>20082</v>
       </c>
       <c r="B1386" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C1386" s="2">
         <v>39</v>
@@ -32733,18 +32734,18 @@
         <v>7</v>
       </c>
       <c r="F1386" s="4">
-        <v>261</v>
+        <v>499.2</v>
       </c>
       <c r="G1386" s="5">
-        <v>46297</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="1387" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1387" s="2">
-        <v>20088</v>
+        <v>20082</v>
       </c>
       <c r="B1387" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C1387" s="2">
         <v>39</v>
@@ -32756,18 +32757,18 @@
         <v>7</v>
       </c>
       <c r="F1387" s="4">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="G1387" s="5">
-        <v>46297</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="1388" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1388" s="2">
-        <v>20098</v>
+        <v>20082</v>
       </c>
       <c r="B1388" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C1388" s="2">
         <v>39</v>
@@ -32779,18 +32780,18 @@
         <v>7</v>
       </c>
       <c r="F1388" s="4">
-        <v>198</v>
+        <v>500</v>
       </c>
       <c r="G1388" s="5">
-        <v>46265</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="1389" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1389" s="2">
-        <v>20100</v>
+        <v>20082</v>
       </c>
       <c r="B1389" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C1389" s="2">
         <v>39</v>
@@ -32802,18 +32803,18 @@
         <v>7</v>
       </c>
       <c r="F1389" s="4">
-        <v>198</v>
+        <v>510</v>
       </c>
       <c r="G1389" s="5">
-        <v>46268</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="1390" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1390" s="2">
-        <v>20100</v>
+        <v>20082</v>
       </c>
       <c r="B1390" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C1390" s="2">
         <v>39</v>
@@ -32825,18 +32826,18 @@
         <v>7</v>
       </c>
       <c r="F1390" s="4">
-        <v>396</v>
+        <v>513.6</v>
       </c>
       <c r="G1390" s="5">
-        <v>46269</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="1391" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1391" s="2">
-        <v>20102</v>
+        <v>20082</v>
       </c>
       <c r="B1391" s="3" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="C1391" s="2">
         <v>39</v>
@@ -32848,18 +32849,18 @@
         <v>7</v>
       </c>
       <c r="F1391" s="4">
-        <v>200</v>
+        <v>514</v>
       </c>
       <c r="G1391" s="5">
-        <v>46276</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="1392" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1392" s="2">
-        <v>20103</v>
+        <v>20082</v>
       </c>
       <c r="B1392" s="3" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C1392" s="2">
         <v>39</v>
@@ -32871,18 +32872,18 @@
         <v>7</v>
       </c>
       <c r="F1392" s="4">
-        <v>118</v>
+        <v>517</v>
       </c>
       <c r="G1392" s="5">
-        <v>46276</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="1393" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1393" s="2">
-        <v>20104</v>
+        <v>20082</v>
       </c>
       <c r="B1393" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C1393" s="2">
         <v>39</v>
@@ -32894,18 +32895,18 @@
         <v>7</v>
       </c>
       <c r="F1393" s="4">
-        <v>2</v>
+        <v>633</v>
       </c>
       <c r="G1393" s="5">
-        <v>46280</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="1394" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1394" s="2">
-        <v>20104</v>
+        <v>20082</v>
       </c>
       <c r="B1394" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C1394" s="2">
         <v>39</v>
@@ -32917,18 +32918,18 @@
         <v>7</v>
       </c>
       <c r="F1394" s="4">
-        <v>6</v>
+        <v>795.2</v>
       </c>
       <c r="G1394" s="5">
-        <v>46268</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="1395" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1395" s="2">
-        <v>20104</v>
+        <v>20082</v>
       </c>
       <c r="B1395" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C1395" s="2">
         <v>39</v>
@@ -32940,18 +32941,18 @@
         <v>7</v>
       </c>
       <c r="F1395" s="4">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="G1395" s="5">
-        <v>46288</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1396" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1396" s="2">
-        <v>20104</v>
+        <v>20084</v>
       </c>
       <c r="B1396" s="3" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="C1396" s="2">
         <v>39</v>
@@ -32963,18 +32964,18 @@
         <v>7</v>
       </c>
       <c r="F1396" s="4">
-        <v>293</v>
+        <v>3</v>
       </c>
       <c r="G1396" s="5">
-        <v>46288</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="1397" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1397" s="2">
-        <v>20104</v>
+        <v>20084</v>
       </c>
       <c r="B1397" s="3" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="C1397" s="2">
         <v>39</v>
@@ -32986,18 +32987,18 @@
         <v>7</v>
       </c>
       <c r="F1397" s="4">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="G1397" s="5">
-        <v>46280</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="1398" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1398" s="2">
-        <v>20104</v>
+        <v>20084</v>
       </c>
       <c r="B1398" s="3" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="C1398" s="2">
         <v>39</v>
@@ -33009,18 +33010,18 @@
         <v>7</v>
       </c>
       <c r="F1398" s="4">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="G1398" s="5">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="1399" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1399" s="2">
-        <v>20104</v>
+        <v>20084</v>
       </c>
       <c r="B1399" s="3" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="C1399" s="2">
         <v>39</v>
@@ -33032,18 +33033,18 @@
         <v>7</v>
       </c>
       <c r="F1399" s="4">
-        <v>392</v>
+        <v>997</v>
       </c>
       <c r="G1399" s="5">
-        <v>46268</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="1400" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1400" s="2">
-        <v>20104</v>
+        <v>20088</v>
       </c>
       <c r="B1400" s="3" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="C1400" s="2">
         <v>39</v>
@@ -33055,18 +33056,18 @@
         <v>7</v>
       </c>
       <c r="F1400" s="4">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="G1400" s="5">
-        <v>46297</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1401" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1401" s="2">
-        <v>20104</v>
+        <v>20088</v>
       </c>
       <c r="B1401" s="3" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="C1401" s="2">
         <v>39</v>
@@ -33078,18 +33079,18 @@
         <v>7</v>
       </c>
       <c r="F1401" s="4">
-        <v>498</v>
+        <v>217</v>
       </c>
       <c r="G1401" s="5">
-        <v>46280</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="1402" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1402" s="2">
-        <v>20104</v>
+        <v>20088</v>
       </c>
       <c r="B1402" s="3" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="C1402" s="2">
         <v>39</v>
@@ -33101,18 +33102,18 @@
         <v>7</v>
       </c>
       <c r="F1402" s="4">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="G1402" s="5">
-        <v>46288</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="1403" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1403" s="2">
-        <v>20104</v>
+        <v>20088</v>
       </c>
       <c r="B1403" s="3" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="C1403" s="2">
         <v>39</v>
@@ -33124,18 +33125,18 @@
         <v>7</v>
       </c>
       <c r="F1403" s="4">
-        <v>512</v>
+        <v>279</v>
       </c>
       <c r="G1403" s="5">
-        <v>46300</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1404" s="2">
-        <v>20104</v>
+        <v>20088</v>
       </c>
       <c r="B1404" s="3" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="C1404" s="2">
         <v>39</v>
@@ -33147,18 +33148,18 @@
         <v>7</v>
       </c>
       <c r="F1404" s="4">
-        <v>1990</v>
+        <v>313</v>
       </c>
       <c r="G1404" s="5">
-        <v>46266</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1405" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1405" s="2">
-        <v>20105</v>
+        <v>20088</v>
       </c>
       <c r="B1405" s="3" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="C1405" s="2">
         <v>39</v>
@@ -33170,18 +33171,18 @@
         <v>7</v>
       </c>
       <c r="F1405" s="4">
-        <v>1000</v>
+        <v>517</v>
       </c>
       <c r="G1405" s="5">
-        <v>46265</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="1406" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1406" s="2">
-        <v>20106</v>
+        <v>20098</v>
       </c>
       <c r="B1406" s="3" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="C1406" s="2">
         <v>39</v>
@@ -33193,18 +33194,18 @@
         <v>7</v>
       </c>
       <c r="F1406" s="4">
-        <v>300</v>
+        <v>198</v>
       </c>
       <c r="G1406" s="5">
-        <v>46280</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="1407" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1407" s="2">
-        <v>900012</v>
+        <v>20100</v>
       </c>
       <c r="B1407" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C1407" s="2">
         <v>39</v>
@@ -33216,18 +33217,18 @@
         <v>7</v>
       </c>
       <c r="F1407" s="4">
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="G1407" s="5">
-        <v>46244</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="1408" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1408" s="2">
-        <v>900018</v>
+        <v>20100</v>
       </c>
       <c r="B1408" s="3" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="C1408" s="2">
         <v>39</v>
@@ -33239,18 +33240,18 @@
         <v>7</v>
       </c>
       <c r="F1408" s="4">
-        <v>18.5</v>
+        <v>396</v>
       </c>
       <c r="G1408" s="5">
-        <v>46031</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="1409" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1409" s="2">
-        <v>900018</v>
+        <v>20102</v>
       </c>
       <c r="B1409" s="3" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="C1409" s="2">
         <v>39</v>
@@ -33262,18 +33263,18 @@
         <v>7</v>
       </c>
       <c r="F1409" s="4">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="G1409" s="5">
-        <v>46248</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="1410" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1410" s="2">
-        <v>900018</v>
+        <v>20103</v>
       </c>
       <c r="B1410" s="3" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="C1410" s="2">
         <v>39</v>
@@ -33285,18 +33286,18 @@
         <v>7</v>
       </c>
       <c r="F1410" s="4">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G1410" s="5">
-        <v>46248</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="1411" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1411" s="2">
-        <v>900019</v>
+        <v>20104</v>
       </c>
       <c r="B1411" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C1411" s="2">
         <v>39</v>
@@ -33308,18 +33309,18 @@
         <v>7</v>
       </c>
       <c r="F1411" s="4">
-        <v>19.5</v>
+        <v>2</v>
       </c>
       <c r="G1411" s="5">
-        <v>46031</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="1412" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1412" s="2">
-        <v>900019</v>
+        <v>20104</v>
       </c>
       <c r="B1412" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C1412" s="2">
         <v>39</v>
@@ -33331,18 +33332,18 @@
         <v>7</v>
       </c>
       <c r="F1412" s="4">
-        <v>148</v>
+        <v>6</v>
       </c>
       <c r="G1412" s="5">
-        <v>46248</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="1413" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1413" s="2">
-        <v>900020</v>
+        <v>20104</v>
       </c>
       <c r="B1413" s="3" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C1413" s="2">
         <v>39</v>
@@ -33354,18 +33355,18 @@
         <v>7</v>
       </c>
       <c r="F1413" s="4">
-        <v>18.5</v>
+        <v>116</v>
       </c>
       <c r="G1413" s="5">
-        <v>46031</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1414" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1414" s="2">
-        <v>900021</v>
+        <v>20104</v>
       </c>
       <c r="B1414" s="3" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C1414" s="2">
         <v>39</v>
@@ -33377,18 +33378,18 @@
         <v>7</v>
       </c>
       <c r="F1414" s="4">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="G1414" s="5">
-        <v>46031</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="1415" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1415" s="2">
-        <v>900022</v>
+        <v>20104</v>
       </c>
       <c r="B1415" s="3" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C1415" s="2">
         <v>39</v>
@@ -33400,18 +33401,18 @@
         <v>7</v>
       </c>
       <c r="F1415" s="4">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="G1415" s="5">
-        <v>46031</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="1416" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1416" s="2">
-        <v>900023</v>
+        <v>20104</v>
       </c>
       <c r="B1416" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C1416" s="2">
         <v>39</v>
@@ -33423,232 +33424,540 @@
         <v>7</v>
       </c>
       <c r="F1416" s="4">
-        <v>19.5</v>
+        <v>300</v>
       </c>
       <c r="G1416" s="5">
-        <v>46035</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="1417" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1417" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1417" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1417" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1417" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1417" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1417" s="4">
+        <v>357</v>
+      </c>
+      <c r="G1417" s="5">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1418" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1418" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1418" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1418" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1418" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1418" s="4">
+        <v>362</v>
+      </c>
+      <c r="G1418" s="5">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1419" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1419" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1419" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1419" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1419" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1419" s="4">
+        <v>392</v>
+      </c>
+      <c r="G1419" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1420" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1420" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1420" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1420" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1420" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1420" s="4">
+        <v>400</v>
+      </c>
+      <c r="G1420" s="5">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1421" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1421" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1421" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1421" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1421" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1421" s="4">
+        <v>414</v>
+      </c>
+      <c r="G1421" s="5">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1422" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1422" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1422" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1422" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1422" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1422" s="4">
+        <v>498</v>
+      </c>
+      <c r="G1422" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1423" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1423" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1423" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1423" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1423" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1423" s="4">
+        <v>506</v>
+      </c>
+      <c r="G1423" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1424" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1424" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1424" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1424" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1424" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1424" s="4">
+        <v>512</v>
+      </c>
+      <c r="G1424" s="5">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1425" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1425" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1425" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1425" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1425" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1425" s="4">
+        <v>519</v>
+      </c>
+      <c r="G1425" s="5">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1426" s="2">
+        <v>20104</v>
+      </c>
+      <c r="B1426" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1426" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1426" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1426" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1426" s="4">
+        <v>1990</v>
+      </c>
+      <c r="G1426" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1427" s="2">
+        <v>20105</v>
+      </c>
+      <c r="B1427" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1427" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1427" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1427" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1427" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G1427" s="5">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1428" s="2">
+        <v>20106</v>
+      </c>
+      <c r="B1428" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1428" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1428" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1428" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1428" s="4">
+        <v>300</v>
+      </c>
+      <c r="G1428" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1429" s="2">
+        <v>900012</v>
+      </c>
+      <c r="B1429" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1429" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1429" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1429" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1429" s="4">
+        <v>40</v>
+      </c>
+      <c r="G1429" s="5">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1430" s="2">
+        <v>900018</v>
+      </c>
+      <c r="B1430" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1430" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1430" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1430" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1430" s="4">
+        <v>18.5</v>
+      </c>
+      <c r="G1430" s="5">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1431" s="2">
+        <v>900018</v>
+      </c>
+      <c r="B1431" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1431" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1431" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1431" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1431" s="4">
+        <v>78</v>
+      </c>
+      <c r="G1431" s="5">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1432" s="2">
+        <v>900018</v>
+      </c>
+      <c r="B1432" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1432" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1432" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1432" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1432" s="4">
+        <v>121</v>
+      </c>
+      <c r="G1432" s="5">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1433" s="2">
+        <v>900019</v>
+      </c>
+      <c r="B1433" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1433" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1433" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1433" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1433" s="4">
+        <v>19.5</v>
+      </c>
+      <c r="G1433" s="5">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1434" s="2">
+        <v>900019</v>
+      </c>
+      <c r="B1434" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1434" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1434" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1434" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1434" s="4">
+        <v>148</v>
+      </c>
+      <c r="G1434" s="5">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1435" s="2">
+        <v>900020</v>
+      </c>
+      <c r="B1435" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1435" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1435" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1435" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1435" s="4">
+        <v>18.5</v>
+      </c>
+      <c r="G1435" s="5">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1436" s="2">
+        <v>900021</v>
+      </c>
+      <c r="B1436" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1436" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1436" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1436" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1436" s="4">
+        <v>19</v>
+      </c>
+      <c r="G1436" s="5">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1437" s="2">
+        <v>900022</v>
+      </c>
+      <c r="B1437" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1437" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1437" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1437" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1437" s="4">
+        <v>19</v>
+      </c>
+      <c r="G1437" s="5">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1438" s="2">
+        <v>900023</v>
+      </c>
+      <c r="B1438" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1438" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1438" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1438" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1438" s="4">
+        <v>19.5</v>
+      </c>
+      <c r="G1438" s="5">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1439" s="2">
         <v>9000183</v>
       </c>
-      <c r="B1417" s="3" t="s">
+      <c r="B1439" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C1417" s="2">
-        <v>39</v>
-      </c>
-      <c r="D1417" s="2">
-        <v>20</v>
-      </c>
-      <c r="E1417" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1417" s="4">
+      <c r="C1439" s="2">
+        <v>39</v>
+      </c>
+      <c r="D1439" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1439" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1439" s="4">
         <v>84</v>
       </c>
-      <c r="G1417" s="5">
+      <c r="G1439" s="5">
         <v>46262</v>
       </c>
-    </row>
-    <row r="1418" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1418" s="2"/>
-      <c r="B1418" s="3"/>
-      <c r="C1418" s="2"/>
-      <c r="D1418" s="2"/>
-      <c r="E1418" s="3"/>
-      <c r="F1418" s="4"/>
-      <c r="G1418" s="5"/>
-    </row>
-    <row r="1419" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1419" s="2"/>
-      <c r="B1419" s="3"/>
-      <c r="C1419" s="2"/>
-      <c r="D1419" s="2"/>
-      <c r="E1419" s="3"/>
-      <c r="F1419" s="4"/>
-      <c r="G1419" s="5"/>
-    </row>
-    <row r="1420" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1420" s="2"/>
-      <c r="B1420" s="3"/>
-      <c r="C1420" s="2"/>
-      <c r="D1420" s="2"/>
-      <c r="E1420" s="3"/>
-      <c r="F1420" s="4"/>
-      <c r="G1420" s="5"/>
-    </row>
-    <row r="1421" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1421" s="2"/>
-      <c r="B1421" s="3"/>
-      <c r="C1421" s="2"/>
-      <c r="D1421" s="2"/>
-      <c r="E1421" s="3"/>
-      <c r="F1421" s="4"/>
-      <c r="G1421" s="5"/>
-    </row>
-    <row r="1422" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1422" s="2"/>
-      <c r="B1422" s="3"/>
-      <c r="C1422" s="2"/>
-      <c r="D1422" s="2"/>
-      <c r="E1422" s="3"/>
-      <c r="F1422" s="4"/>
-      <c r="G1422" s="5"/>
-    </row>
-    <row r="1423" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1423" s="2"/>
-      <c r="B1423" s="3"/>
-      <c r="C1423" s="2"/>
-      <c r="D1423" s="2"/>
-      <c r="E1423" s="3"/>
-      <c r="F1423" s="4"/>
-      <c r="G1423" s="5"/>
-    </row>
-    <row r="1424" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1424" s="2"/>
-      <c r="B1424" s="3"/>
-      <c r="C1424" s="2"/>
-      <c r="D1424" s="2"/>
-      <c r="E1424" s="3"/>
-      <c r="F1424" s="4"/>
-      <c r="G1424" s="5"/>
-    </row>
-    <row r="1425" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1425" s="2"/>
-      <c r="B1425" s="3"/>
-      <c r="C1425" s="2"/>
-      <c r="D1425" s="2"/>
-      <c r="E1425" s="3"/>
-      <c r="F1425" s="4"/>
-      <c r="G1425" s="5"/>
-    </row>
-    <row r="1426" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1426" s="2"/>
-      <c r="B1426" s="3"/>
-      <c r="C1426" s="2"/>
-      <c r="D1426" s="2"/>
-      <c r="E1426" s="3"/>
-      <c r="F1426" s="4"/>
-      <c r="G1426" s="5"/>
-    </row>
-    <row r="1427" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1427" s="2"/>
-      <c r="B1427" s="3"/>
-      <c r="C1427" s="2"/>
-      <c r="D1427" s="2"/>
-      <c r="E1427" s="3"/>
-      <c r="F1427" s="4"/>
-      <c r="G1427" s="5"/>
-    </row>
-    <row r="1428" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1428" s="2"/>
-      <c r="B1428" s="3"/>
-      <c r="C1428" s="2"/>
-      <c r="D1428" s="2"/>
-      <c r="E1428" s="3"/>
-      <c r="F1428" s="4"/>
-      <c r="G1428" s="5"/>
-    </row>
-    <row r="1429" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1429" s="2"/>
-      <c r="B1429" s="3"/>
-      <c r="C1429" s="2"/>
-      <c r="D1429" s="2"/>
-      <c r="E1429" s="3"/>
-      <c r="F1429" s="4"/>
-      <c r="G1429" s="5"/>
-    </row>
-    <row r="1430" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1430" s="2"/>
-      <c r="B1430" s="3"/>
-      <c r="C1430" s="2"/>
-      <c r="D1430" s="2"/>
-      <c r="E1430" s="3"/>
-      <c r="F1430" s="4"/>
-      <c r="G1430" s="5"/>
-    </row>
-    <row r="1431" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1431" s="2"/>
-      <c r="B1431" s="3"/>
-      <c r="C1431" s="2"/>
-      <c r="D1431" s="2"/>
-      <c r="E1431" s="3"/>
-      <c r="F1431" s="4"/>
-      <c r="G1431" s="5"/>
-    </row>
-    <row r="1432" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1432" s="2"/>
-      <c r="B1432" s="3"/>
-      <c r="C1432" s="2"/>
-      <c r="D1432" s="2"/>
-      <c r="E1432" s="3"/>
-      <c r="F1432" s="4"/>
-      <c r="G1432" s="5"/>
-    </row>
-    <row r="1433" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1433" s="2"/>
-      <c r="B1433" s="3"/>
-      <c r="C1433" s="2"/>
-      <c r="D1433" s="2"/>
-      <c r="E1433" s="3"/>
-      <c r="F1433" s="4"/>
-      <c r="G1433" s="5"/>
-    </row>
-    <row r="1434" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1434" s="2"/>
-      <c r="B1434" s="3"/>
-      <c r="C1434" s="2"/>
-      <c r="D1434" s="2"/>
-      <c r="E1434" s="3"/>
-      <c r="F1434" s="4"/>
-      <c r="G1434" s="5"/>
-    </row>
-    <row r="1435" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1435" s="2"/>
-      <c r="B1435" s="3"/>
-      <c r="C1435" s="2"/>
-      <c r="D1435" s="2"/>
-      <c r="E1435" s="3"/>
-      <c r="F1435" s="4"/>
-      <c r="G1435" s="5"/>
-    </row>
-    <row r="1436" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1436" s="2"/>
-      <c r="B1436" s="3"/>
-      <c r="C1436" s="2"/>
-      <c r="D1436" s="2"/>
-      <c r="E1436" s="3"/>
-      <c r="F1436" s="4"/>
-      <c r="G1436" s="5"/>
-    </row>
-    <row r="1437" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1437" s="2"/>
-      <c r="B1437" s="3"/>
-      <c r="C1437" s="2"/>
-      <c r="D1437" s="2"/>
-      <c r="E1437" s="3"/>
-      <c r="F1437" s="4"/>
-      <c r="G1437" s="5"/>
-    </row>
-    <row r="1438" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1438" s="2"/>
-      <c r="B1438" s="3"/>
-      <c r="C1438" s="2"/>
-      <c r="D1438" s="2"/>
-      <c r="E1438" s="3"/>
-      <c r="F1438" s="4"/>
-      <c r="G1438" s="5"/>
-    </row>
-    <row r="1439" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1439" s="2"/>
-      <c r="B1439" s="3"/>
-      <c r="C1439" s="2"/>
-      <c r="D1439" s="2"/>
-      <c r="E1439" s="3"/>
-      <c r="F1439" s="4"/>
-      <c r="G1439" s="5"/>
     </row>
     <row r="1440" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1440" s="2"/>
